--- a/registration_forms/023_predictive_reordering_pilot_registration--registration_forms.xlsx
+++ b/registration_forms/023_predictive_reordering_pilot_registration--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1053,8 +1053,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'saas'}</t>
+          <t>saas</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'SaaS'}</t>
+          <t>SaaS</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'operations'}</t>
+          <t>operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Operations'}</t>
+          <t>Operations</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'0-10'}</t>
+          <t>0-10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': '0-10'}</t>
+          <t>0-10</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'11-50'}</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': '11-50'}</t>
+          <t>11-50</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'51-100'}</t>
+          <t>51-100</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': '51-100'}</t>
+          <t>51-100</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'101-500'}</t>
+          <t>101-500</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': '101-500'}</t>
+          <t>101-500</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'501+'}</t>
+          <t>501+</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': '501+'}</t>
+          <t>501+</t>
         </is>
       </c>
     </row>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'alabama'}</t>
+          <t>alabama</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Alabama'}</t>
+          <t>Alabama</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'alaska'}</t>
+          <t>alaska</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Alaska'}</t>
+          <t>Alaska</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'arizona'}</t>
+          <t>arizona</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Arizona'}</t>
+          <t>Arizona</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'arkansas'}</t>
+          <t>arkansas</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Arkansas'}</t>
+          <t>Arkansas</t>
         </is>
       </c>
     </row>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'california'}</t>
+          <t>california</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'California'}</t>
+          <t>California</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'colorado'}</t>
+          <t>colorado</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'Colorado'}</t>
+          <t>Colorado</t>
         </is>
       </c>
     </row>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'connecticut'}</t>
+          <t>connecticut</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'Connecticut'}</t>
+          <t>Connecticut</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1371,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'delaware'}</t>
+          <t>delaware</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'Delaware'}</t>
+          <t>Delaware</t>
         </is>
       </c>
     </row>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'florida'}</t>
+          <t>florida</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'Florida'}</t>
+          <t>Florida</t>
         </is>
       </c>
     </row>
@@ -1405,12 +1405,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'georgia'}</t>
+          <t>georgia</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'Georgia'}</t>
+          <t>Georgia</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1422,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'hawaii'}</t>
+          <t>hawaii</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'Hawaii'}</t>
+          <t>Hawaii</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'idaho'}</t>
+          <t>idaho</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'Idaho'}</t>
+          <t>Idaho</t>
         </is>
       </c>
     </row>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'illinois'}</t>
+          <t>illinois</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'Illinois'}</t>
+          <t>Illinois</t>
         </is>
       </c>
     </row>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'indiana'}</t>
+          <t>indiana</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'Indiana'}</t>
+          <t>Indiana</t>
         </is>
       </c>
     </row>
@@ -1490,12 +1490,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_'iowa'}</t>
+          <t>iowa</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': 'Iowa'}</t>
+          <t>Iowa</t>
         </is>
       </c>
     </row>
@@ -1507,12 +1507,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_16,_'name':_'kansas'}</t>
+          <t>kansas</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 16, 'name': 'Kansas'}</t>
+          <t>Kansas</t>
         </is>
       </c>
     </row>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_17,_'name':_'kentucky'}</t>
+          <t>kentucky</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 17, 'name': 'Kentucky'}</t>
+          <t>Kentucky</t>
         </is>
       </c>
     </row>
@@ -1541,12 +1541,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_18,_'name':_'louisiana'}</t>
+          <t>louisiana</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 18, 'name': 'Louisiana'}</t>
+          <t>Louisiana</t>
         </is>
       </c>
     </row>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_19,_'name':_'maine'}</t>
+          <t>maine</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 19, 'name': 'Maine'}</t>
+          <t>Maine</t>
         </is>
       </c>
     </row>
@@ -1575,12 +1575,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_20,_'name':_'maryland'}</t>
+          <t>maryland</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 20, 'name': 'Maryland'}</t>
+          <t>Maryland</t>
         </is>
       </c>
     </row>
@@ -1592,12 +1592,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_21,_'name':_'massachusetts'}</t>
+          <t>massachusetts</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 21, 'name': 'Massachusetts'}</t>
+          <t>Massachusetts</t>
         </is>
       </c>
     </row>
@@ -1609,12 +1609,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_22,_'name':_'michigan'}</t>
+          <t>michigan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 22, 'name': 'Michigan'}</t>
+          <t>Michigan</t>
         </is>
       </c>
     </row>
@@ -1626,12 +1626,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_23,_'name':_'minnesota'}</t>
+          <t>minnesota</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 23, 'name': 'Minnesota'}</t>
+          <t>Minnesota</t>
         </is>
       </c>
     </row>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_24,_'name':_'mississippi'}</t>
+          <t>mississippi</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 24, 'name': 'Mississippi'}</t>
+          <t>Mississippi</t>
         </is>
       </c>
     </row>
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_25,_'name':_'missouri'}</t>
+          <t>missouri</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 25, 'name': 'Missouri'}</t>
+          <t>Missouri</t>
         </is>
       </c>
     </row>
@@ -1677,12 +1677,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_26,_'name':_'montana'}</t>
+          <t>montana</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 26, 'name': 'Montana'}</t>
+          <t>Montana</t>
         </is>
       </c>
     </row>
@@ -1694,12 +1694,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_27,_'name':_'nebraska'}</t>
+          <t>nebraska</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 27, 'name': 'Nebraska'}</t>
+          <t>Nebraska</t>
         </is>
       </c>
     </row>
@@ -1711,12 +1711,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_28,_'name':_'nevada'}</t>
+          <t>nevada</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 28, 'name': 'Nevada'}</t>
+          <t>Nevada</t>
         </is>
       </c>
     </row>
@@ -1728,12 +1728,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_29,_'name':_'new_hampshire'}</t>
+          <t>new_hampshire</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 29, 'name': 'New Hampshire'}</t>
+          <t>New Hampshire</t>
         </is>
       </c>
     </row>
@@ -1745,12 +1745,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_30,_'name':_'new_jersey'}</t>
+          <t>new_jersey</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 30, 'name': 'New Jersey'}</t>
+          <t>New Jersey</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_31,_'name':_'new_mexico'}</t>
+          <t>new_mexico</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 31, 'name': 'New Mexico'}</t>
+          <t>New Mexico</t>
         </is>
       </c>
     </row>
@@ -1779,12 +1779,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_32,_'name':_'new_york'}</t>
+          <t>new_york</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 32, 'name': 'New York'}</t>
+          <t>New York</t>
         </is>
       </c>
     </row>
@@ -1796,12 +1796,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_33,_'name':_'north_carolina'}</t>
+          <t>north_carolina</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 33, 'name': 'North Carolina'}</t>
+          <t>North Carolina</t>
         </is>
       </c>
     </row>
@@ -1813,12 +1813,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_34,_'name':_'north_dakota'}</t>
+          <t>north_dakota</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 34, 'name': 'North Dakota'}</t>
+          <t>North Dakota</t>
         </is>
       </c>
     </row>
@@ -1830,12 +1830,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_35,_'name':_'ohio'}</t>
+          <t>ohio</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 35, 'name': 'Ohio'}</t>
+          <t>Ohio</t>
         </is>
       </c>
     </row>
@@ -1847,12 +1847,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_36,_'name':_'oklahoma'}</t>
+          <t>oklahoma</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 36, 'name': 'Oklahoma'}</t>
+          <t>Oklahoma</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_37,_'name':_'oregon'}</t>
+          <t>oregon</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 37, 'name': 'Oregon'}</t>
+          <t>Oregon</t>
         </is>
       </c>
     </row>
@@ -1881,12 +1881,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_38,_'name':_'pennsylvania'}</t>
+          <t>pennsylvania</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 38, 'name': 'Pennsylvania'}</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
     </row>
@@ -1898,12 +1898,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_39,_'name':_'rhode_island'}</t>
+          <t>rhode_island</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': 39, 'name': 'Rhode Island'}</t>
+          <t>Rhode Island</t>
         </is>
       </c>
     </row>
@@ -1915,12 +1915,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'id':_40,_'name':_'south_carolina'}</t>
+          <t>south_carolina</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'id': 40, 'name': 'South Carolina'}</t>
+          <t>South Carolina</t>
         </is>
       </c>
     </row>
@@ -1932,12 +1932,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'id':_41,_'name':_'south_dakota'}</t>
+          <t>south_dakota</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'id': 41, 'name': 'South Dakota'}</t>
+          <t>South Dakota</t>
         </is>
       </c>
     </row>
@@ -1949,12 +1949,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'id':_42,_'name':_'tennessee'}</t>
+          <t>tennessee</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'id': 42, 'name': 'Tennessee'}</t>
+          <t>Tennessee</t>
         </is>
       </c>
     </row>
@@ -1966,12 +1966,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'id':_43,_'name':_'texas'}</t>
+          <t>texas</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'id': 43, 'name': 'Texas'}</t>
+          <t>Texas</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'id':_44,_'name':_'utah'}</t>
+          <t>utah</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'id': 44, 'name': 'Utah'}</t>
+          <t>Utah</t>
         </is>
       </c>
     </row>
@@ -2000,12 +2000,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'id':_45,_'name':_'vermont'}</t>
+          <t>vermont</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'id': 45, 'name': 'Vermont'}</t>
+          <t>Vermont</t>
         </is>
       </c>
     </row>
@@ -2017,12 +2017,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'id':_46,_'name':_'virginia'}</t>
+          <t>virginia</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'id': 46, 'name': 'Virginia'}</t>
+          <t>Virginia</t>
         </is>
       </c>
     </row>
@@ -2034,12 +2034,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'id':_47,_'name':_'washington'}</t>
+          <t>washington</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'id': 47, 'name': 'Washington'}</t>
+          <t>Washington</t>
         </is>
       </c>
     </row>
@@ -2051,12 +2051,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'id':_48,_'name':_'west_virginia'}</t>
+          <t>west_virginia</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'id': 48, 'name': 'West Virginia'}</t>
+          <t>West Virginia</t>
         </is>
       </c>
     </row>
@@ -2068,12 +2068,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'id':_49,_'name':_'wisconsin'}</t>
+          <t>wisconsin</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'id': 49, 'name': 'Wisconsin'}</t>
+          <t>Wisconsin</t>
         </is>
       </c>
     </row>
@@ -2085,12 +2085,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'id':_50,_'name':_'wyoming'}</t>
+          <t>wyoming</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'id': 50, 'name': 'Wyoming'}</t>
+          <t>Wyoming</t>
         </is>
       </c>
     </row>
